--- a/controller BOM.xlsx
+++ b/controller BOM.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25516"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="26207"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allan/Desktop/yahrzeit/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="540" yWindow="-20" windowWidth="27940" windowHeight="17520" tabRatio="500"/>
+    <workbookView xWindow="540" yWindow="460" windowWidth="27940" windowHeight="17520" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Exch_Rate">Sheet1!$E$7</definedName>
+    <definedName name="Exch_Rate">Sheet1!$D$7</definedName>
   </definedNames>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="150001" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -22,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Costed Bill of Materials</t>
   </si>
@@ -42,30 +47,9 @@
     <t>Arduino Ethernet</t>
   </si>
   <si>
-    <t>Proto Board</t>
-  </si>
-  <si>
-    <t>pins</t>
-  </si>
-  <si>
-    <t>IDC socket</t>
-  </si>
-  <si>
-    <t>Project Box</t>
-  </si>
-  <si>
     <t>Exchange Rt</t>
   </si>
   <si>
-    <t>cable connectors pair</t>
-  </si>
-  <si>
-    <t>ribbon cable</t>
-  </si>
-  <si>
-    <t>wire &amp; solder</t>
-  </si>
-  <si>
     <t>NIS</t>
   </si>
   <si>
@@ -75,20 +59,60 @@
     <t>Cost ea</t>
   </si>
   <si>
-    <t>cost, Lot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Cost </t>
+    <t>Mini Shield design consulting</t>
+  </si>
+  <si>
+    <t>Apple Thunderbold Gigabit Ethernet</t>
+  </si>
+  <si>
+    <t>Travel Expenses</t>
+  </si>
+  <si>
+    <t>no charge for airfare or hotel</t>
+  </si>
+  <si>
+    <t>lab supplies: protoboard, pins, wire, solder, 10-pin IDC sockets, ribbon cable</t>
+  </si>
+  <si>
+    <t>Mini Shield FAB, with shipping</t>
+  </si>
+  <si>
+    <t>other expenses, included meals, gas</t>
+  </si>
+  <si>
+    <t>power supply</t>
+  </si>
+  <si>
+    <t>enclosure</t>
+  </si>
+  <si>
+    <t>Material Costs for Embedded Controller</t>
+  </si>
+  <si>
+    <t>subtotal</t>
+  </si>
+  <si>
+    <t>total invoice</t>
+  </si>
+  <si>
+    <t>Other project costs:</t>
+  </si>
+  <si>
+    <t>Consulting Fee, July 27, 2015</t>
+  </si>
+  <si>
+    <t>Car Rental prorated 1/10 of 462.12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$₪-40D]\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -118,6 +142,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,10 +200,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -161,6 +236,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -486,245 +566,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
-        <v>42188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>42217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7">
+      <c r="C6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C7" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="14">
         <v>3.85</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="E7" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="7">
         <v>269</v>
       </c>
-      <c r="D9" s="2">
-        <f>C9/Exch_Rate</f>
-        <v>69.870129870129873</v>
-      </c>
-      <c r="F9" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>269</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <f>C10/Exch_Rate</f>
         <v>69.870129870129873</v>
       </c>
-      <c r="F10" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>99</v>
-      </c>
-      <c r="C11">
-        <f>B11/3</f>
-        <v>33</v>
-      </c>
-      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7">
+        <v>229</v>
+      </c>
+      <c r="E11" s="2">
         <f>C11/Exch_Rate</f>
-        <v>8.5714285714285712</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>59.480519480519476</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7">
         <v>118</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <f>C12/Exch_Rate</f>
         <v>30.649350649350648</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="9">
+        <f>SUM(C10:C13)</f>
+        <v>616</v>
+      </c>
+      <c r="E15" s="6">
+        <f>C15/Exch_Rate</f>
+        <v>160</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E20" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2">
-        <f>C13/Exch_Rate</f>
-        <v>1.2987012987012987</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2">
-        <f>C14/Exch_Rate</f>
-        <v>1.2987012987012987</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="E21" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>32.880000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2">
+        <v>31.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="E25" s="6">
+        <f>SUM(E20:E23)</f>
+        <v>125.41999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B15">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
-        <f>C15/Exch_Rate</f>
-        <v>1.2987012987012987</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B16">
-        <v>30</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2">
-        <f>C16/Exch_Rate</f>
-        <v>2.5974025974025974</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <f>C17/Exch_Rate</f>
-        <v>1.2987012987012987</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="D18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="C19">
-        <f>SUM(C9:C17)</f>
-        <v>719</v>
-      </c>
-      <c r="D19" s="2">
-        <f>C19/Exch_Rate</f>
-        <v>186.75324675324674</v>
-      </c>
-      <c r="F19" s="2">
-        <f>SUM(F9:F17)</f>
-        <v>46</v>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="2">
+        <v>46.12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="E32" s="6">
+        <f>SUM(E28:E30)</f>
+        <v>114.12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="E36" s="13">
+        <f>E15+E25+E32+E34</f>
+        <v>899.54</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>